--- a/examples/reports/MRB_Report_Adapted.xlsx
+++ b/examples/reports/MRB_Report_Adapted.xlsx
@@ -685,12 +685,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>1.740e-03</t>
+          <t>4.807e-04</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>3.52e-04</t>
+          <t>3.65e-04</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>6.857e-04</t>
+          <t>5.298e-04</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2.95e-04</t>
+          <t>3.33e-04</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.769e-02</t>
+          <t>1.741e-02</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1.89e-04</t>
+          <t>1.77e-04</t>
         </is>
       </c>
     </row>
